--- a/artfynd/A 15146-2024 artfynd.xlsx
+++ b/artfynd/A 15146-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>109427542</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544779.9513086724</v>
+        <v>544780</v>
       </c>
       <c r="R2" t="n">
-        <v>6959750.365982523</v>
+        <v>6959751</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +775,11 @@
         <v>109427543</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544481.7757323799</v>
+        <v>544482</v>
       </c>
       <c r="R3" t="n">
-        <v>6959784.798921763</v>
+        <v>6959785</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2023-05-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +866,394 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109427546</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>544456</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6959759</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>109427547</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>544456</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6959759</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109427545</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>544456</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6959759</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>109427544</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrkrången, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>544456</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6959759</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Louise Almén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15146-2024 artfynd.xlsx
+++ b/artfynd/A 15146-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109427542</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109427543</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109427546</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109427547</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109427545</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109427544</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>